--- a/important_mails_2026-06-13.xlsx
+++ b/important_mails_2026-06-13.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H269"/>
+  <dimension ref="A1:H261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5385,7 +5385,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5400,79 +5400,21 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 02:39:33 +0000</t>
+          <t>Sat, 6 Jun 2026 13:21:50 +0000</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
+          <t>Your payment is on the way</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed and shipped your removal
-request (ZazNpo+O9J) to the address you specified before.
-Return Summary:
-Quantity Requested: 1
-Quantity Successfully Shipped: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being shipped, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-3833131-7439462
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-633320912879363</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 6 Jun 2026 13:21:50 +0000</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5492,39 +5434,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:46 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5541,39 +5483,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 15:15:46 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5593,39 +5535,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5642,39 +5584,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5694,39 +5636,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:36 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5746,39 +5688,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5798,39 +5740,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 14:37:25 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5847,39 +5789,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5899,39 +5841,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:43:44 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5951,39 +5893,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:42:27 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6003,39 +5945,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 14:51:20 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -6051,39 +5993,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 13:35:40 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6100,39 +6042,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 14:39:47 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6152,39 +6094,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:30:35 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6204,39 +6146,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:29:45 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6253,39 +6195,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6305,39 +6247,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6357,39 +6299,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -6406,39 +6348,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -6455,39 +6397,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6507,39 +6449,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -6563,39 +6505,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -6619,39 +6561,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6671,39 +6613,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6723,39 +6665,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6775,39 +6717,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6827,188 +6769,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 14:51:22 +0000</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 5 Jun 2026 19:25:12 +0000</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>Twoja płatność jest już w drodze</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>96
-Ten tytuł będzie wyświetlany na urządzeniach mobilnych
- Gratulujemy! Twoja płatność jest już w drodze, a środki powinny wkrótce do Ciebie dotrzeć.
- Próba wypłaty środków
-Gratulacje, Weihai EU! Twoja płatność jest już w drodze, a środki powinny do Ciebie dotrzeć w terminie od trzech do pięciu dni.
-Dnia 05/14/26 14:51 CEST zainicjowaliśmy przelew na kwotę PLN
- 204.22 na konto powiązane z Twoją metodą płatności (rachunek bankowy o ostatnich cyfrach 229).
- Jeśli kwota jest mniejsza niż oczekiwana, oto kilka kwestii do wzięcia pod uwagę:
- Czy Twoje saldo jest niedostępne? Amazon może zatrzymać środki na pokrycie ewentualnych kosztów zwrotów towarów, roszczeń i obciążeń zwrotnych od kupujących. W takim przypadku saldo zamknięcia w raporcie płatności pokaże niedostępne saldo na zarezerwowaną w tym celu kwotę.
- Czy Twoja sprzedaż wystarczyła na pokrycie wszystkich opłat i zwrotów w tym okresie rozliczeniowym? Kwota płatności uwzględnia koszt działań sprzedażowych, opłaty za sprzedaż oraz opłaty za promocje i usługi. Aby lepiej zrozumieć wysokość salda zamknięcia, warto przeanalizować raport płatności, który znajdziesz w Seller Central w karcie „Raporty”.
-Więcej o raportach płatności w S</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 14:50:04 +0000</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 05/14/26 14:49 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 296,54.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 14:49:55 +0000</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 05/14/26 14:49 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 762.53.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 5 Jun 2026 19:25:12 +0000</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7026,39 +6819,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 03:06:03 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -7078,39 +6871,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:23:36 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7128,39 +6921,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:17:04 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7178,39 +6971,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:40:15 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -7226,39 +7019,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:33:38 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -7277,39 +7070,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 21:10:43 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7327,39 +7120,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:18:22 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7377,39 +7170,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:35 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7427,39 +7220,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 02:36:04 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册
@@ -7494,39 +7287,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 12:53:21 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -7542,40 +7335,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 10:39:43 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.se" &lt;cscompliance-docreview-seller@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review
@@ -7592,40 +7385,40 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:31:42 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS -
  APPEAL</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS - APPEAL
@@ -7646,39 +7439,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:48 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7696,39 +7489,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:09:04 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7746,39 +7539,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:43 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7796,39 +7589,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:21 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7846,39 +7639,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 06:06:12 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>帮您免费一站式搞定VAT、EPR等合规问题！亚马逊合规服务商城现已正式上线！</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>亚马逊合规服务商城正式上线，一站式帮助卖家高效搞定欧洲站点的VAT、EPR等合规问题。
 			尊敬的 深圳市微海众信科技有限公司,
@@ -7908,39 +7701,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 17:40:38 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -7959,40 +7752,40 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 11:02:38 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -8005,40 +7798,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:58:41 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -8055,40 +7848,40 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:53:39 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -8105,40 +7898,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:49:38 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC - DOC REVIEW
@@ -8155,39 +7948,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:02:52 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -8207,40 +8000,40 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:57:24 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -8256,40 +8049,40 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:55:04 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.fr" &lt;cscompliance-docreview-seller@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review
@@ -8305,39 +8098,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -8356,40 +8149,40 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8405,40 +8198,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8452,40 +8245,40 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -8499,40 +8292,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -8545,39 +8338,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -8597,39 +8390,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -8654,96 +8447,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 10:44:21 +0000</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>主题：需要采取的行动：网站禁止的 ASIN</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的卖家，
-我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
-我们建议您提交所需的文件以取消禁止显示您的 ASIN 并激活您的列表。
-以下是您被屏蔽的 ASIN 的示例：
-B0F1R6Y4JL
-如果您想了解当前被禁止的所有 ASIN 以及被禁止的原因，请登录您的卖家中心帐户并转至 “目录“ &gt;&gt; “补全您的草稿“ &gt;&gt;“有问题的已发布商品信息“ &gt;&gt; “详情页面已删除“. 您所有的 ASIN 都将列在这里
-https://sellercentral-europe.amazon.com/fixyourproducts/drafts
-要上传所需文件或提出申诉以解除对 ASIN 的压制，请遵循此路径  登录您的卖家中心账户并前往 “绩效“ &gt;&gt; “帐户健康“ &gt;&gt; “文件要求“ 在下面 “产品合规要求“ 在右下角 &gt;&gt; “提供文件“ 并选择上传文件或上诉。
-https://sellercentral-europe.amazon.com/performance/account/health/compliance-request
-如果您需要进一步的帮助，请通过联系我们提交案例。- https://sellercentral-europe.amazon.com/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
-如果您不是正确的联系人，请将此电子邮件重定向到正确的联系人。
-如果您想退订，请回复所有主题行“退订”
-注意：此电子邮件不受监控，任何有问题的回复都不会得到答复
-请注意，所附表格属于亚马逊机密。不要打扰。
-感谢您在亚马逊商店销售，
-亚马逊购买团队
-在我们的 10 秒调查中分享快速反馈，无需登录供应商/卖家中心。您的意见很重要！
-单击此处，https://amazonexteu.qualtrics.com/jfe/form/SV_didQ0FJXzXequbQ?Condition=Singlelink&amp;caseId=${print-case-id}
-Amazon Services Europe S.à r.l.38 Avenue John F. Kennedy, L-1855 Luxembourg，卢森堡注册编号 B-93815，股本 37,551 欧元，营业执照编号： 132595，卢森堡增值税注册编号 LU 19647148。
-© 2022 Amazon.com Inc. 或其关联公司。保留所有权利</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:59 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8758,39 +8494,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:01:19 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -8808,39 +8544,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 12:36:48 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -8867,39 +8603,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 12:31:12 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -8926,39 +8662,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:43:20 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -8983,39 +8719,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:38:16 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -9040,39 +8776,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:25:17 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -9099,39 +8835,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:21:01 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -9156,39 +8892,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 11:10:07 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -9215,39 +8951,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 10:55:24 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026
  96
@@ -9266,39 +9002,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 10:25:16 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Fulfilled by Amazon for 5/2026
  96
@@ -9317,39 +9053,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 09:33:20 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -9373,39 +9109,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 07:52:40 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Realizacja przez Amazon for 5/2026
  96
@@ -9429,39 +9165,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 07:36:30 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -9488,39 +9224,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:48:36 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -9544,39 +9280,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:24:07 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 5/2026</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.pl Faktura Sprzedawcy for 5/2026
  96
@@ -9601,39 +9337,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 06:01:50 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Verkoper for 5/2026
  96
@@ -9658,39 +9394,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:56:14 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 5/2026
  96
@@ -9708,39 +9444,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:28:55 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 5/2026</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Säljare for 5/2026
  96
@@ -9767,39 +9503,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:23:44 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 5/2026
  96
@@ -9817,39 +9553,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:10:53 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 5/2026</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Verkäufer for 5/2026
  96
@@ -9874,39 +9610,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 05:02:43 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 5/2026</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Vendedor for 5/2026
  96
@@ -9933,39 +9669,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 04:45:31 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 5/2026</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com.be Factuur Verkoper for 5/2026
  96
@@ -9986,39 +9722,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 13:05:07 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -10048,39 +9784,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:43:35 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -10105,39 +9841,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:33:36 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -10164,39 +9900,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:16:55 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -10214,39 +9950,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:09:15 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -10264,39 +10000,39 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:09:08 +0000</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -10320,39 +10056,39 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 11:58:55 +0000</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -10377,39 +10113,39 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 11:38:44 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -10436,40 +10172,40 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 23:11:17 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -10485,40 +10221,40 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 23:10:46 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -10534,39 +10270,39 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:37:38 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -10605,39 +10341,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:31:54 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -10653,39 +10389,39 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:14:06 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -10701,39 +10437,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:10:02 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -10749,40 +10485,40 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:43:42 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -10797,40 +10533,40 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:42:40 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -10844,39 +10580,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:38:41 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -10890,39 +10626,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:37:16 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -10937,39 +10673,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:35:16 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -10983,39 +10719,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:31:58 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -11030,39 +10766,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:35:34 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -11101,39 +10837,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:29:07 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -11149,40 +10885,40 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:25:02 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -11198,39 +10934,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:15:34 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -11244,39 +10980,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:56 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -11292,40 +11028,40 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:34 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -11341,39 +11077,39 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -11389,39 +11125,39 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -11436,39 +11172,39 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 13:54:47 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -11483,39 +11219,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 16:55:18 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>Logística Multicanal de Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Ahorra un 20 % en las tarifas de Logística Multicanal a partir del 25 de junio</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>96
  Ya están disponibles dos nuevos programas de descuentos para los vendedores aptos
@@ -11529,39 +11265,39 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 16:38:54 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale di Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Tariffe di Gestione multicanale: sconto del 20% dal 25 giugno</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>96
  Due nuovi programmi di sconto sono ora disponibili per i venditori idonei
@@ -11575,39 +11311,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 02:40:59 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 05/2026</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -11625,39 +11361,39 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:40 +0000</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -11673,39 +11409,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:32 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -11719,40 +11455,40 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:31 +0000</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -11768,39 +11504,39 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:08:15 +0000</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -11816,40 +11552,40 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 15:14:09 +0000</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -11865,39 +11601,39 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 15:14:03 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -11913,39 +11649,39 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:04 +0000</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -11961,39 +11697,39 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:01 +0000</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -12007,40 +11743,40 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:00 +0000</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -12056,39 +11792,39 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:29 +0000</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -12104,39 +11840,39 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 15:12:02 +0000</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -12152,40 +11888,40 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -12201,39 +11937,39 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 23:39:40 +0000</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para junio</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para junio
@@ -12262,39 +11998,39 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 17:10:26 +0000</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -12310,40 +12046,40 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 15:13:11 +0000</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Tu cuenta cumple ahora nuestros requisitos de registro a efectos
  fiscales en Europa</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -12368,39 +12104,39 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 15:09:37 +0000</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Twoje konto spełnia już europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -12425,39 +12161,39 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 10:15:12 +0000</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -12487,39 +12223,39 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Tue, 26 May 2026 12:22:30 +0000 (UTC)</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>TikTok Shop &lt;tiktokshopseller@shop.tiktok.com&gt;</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>借助这些高潜力商品加速你的业务成长</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>96
  借助这些高潜力商品加速你的业务成长
@@ -12612,39 +12348,39 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 17:10:44 +0000</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -12662,39 +12398,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 08:12:17 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>Il team di Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Nuova convalida dei numeri di spedizione attiva da oggi</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiorniamo i parametri di convalida dei numeri di spedizione per le spedizioni con corrieri non affiliati, includendo controlli relativi alla lunghezza, al formato previsto del corriere e ai requisiti aggiuntivi relativi ai caratteri. Questo ci permetterà di elaborare il tuo inventario più velocemente.
@@ -12705,39 +12441,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 07:52:06 +0000</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Disponible desde hoy la nueva validación del número de seguimiento</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>96
  Hemos añadido parámetros de validación del número de seguimiento en los envíos con transportistas no asociados para comprobar la longitud, formato previsto del transportista y requisitos de caracteres adicionales y así procesar tu inventario más rápido.
@@ -12749,39 +12485,39 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 17:10:56 +0000</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -12797,39 +12533,39 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 08:56:06 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>5月27日前入库助力Prime Day成功</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -12859,39 +12595,39 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:06:09 +0000</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -12906,39 +12642,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 13:00:10 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -12953,39 +12689,39 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 10:15:46 +0000</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -13000,39 +12736,39 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 15:00:47 +0000</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -13047,39 +12783,39 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:37 +0000</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -13094,39 +12830,39 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:10:53 +0000</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -13144,39 +12880,39 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:55:42 +0000</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Ship Smarter: Get 3 FREE Brokerage Fees: Limited Time C2S2 Offer 🚀</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3hy11/6664114770/h/cIM7P1R6ABFsNRmzeIU2ASpTCxzOevVrUjDi2lts12A)
 Ship Cross-Border &amp; Save Big. Get Started with C2S2 Today.
@@ -13193,39 +12929,39 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 06:33:16 +0000</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -13244,39 +12980,39 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:48:46 +0000</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -13291,40 +13027,40 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 05:21:00 +0000</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -13340,39 +13076,39 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 17:10:29 +0000</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -13388,39 +13124,39 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
 EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
@@ -13441,208 +13177,39 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 14:07:42 +0000</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F253" s="2" t="inlineStr">
-        <is>
-          <t>Pagamento elaborato con successo</t>
-        </is>
-      </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-This title will display on mobile devices
- Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
- Tentativo di pagamento
-Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
-In data 05/14/26 14:07 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
- 350,84.
- Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
- Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
- Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 14 May 2026 03:00:00 +0000</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>最大化您的 Prime Day 业绩</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="inlineStr">
-        <is>
-          <t>最大化您的 Prime Day 业绩
-尊敬的卖家，
-为 2026 年 Prime Day做好准备 - 为数百万 Prime 会员打造不容错过的优惠！加入我们今年6月为期4天活动。通过提交促销，确保充足库存，提升曝光度以助力您冲刺最佳业绩！
-关键日期
-活动日期： 2026年6月 (具体日期待公布)
-提报截止日期： 促销 – 2026 年 6 月 19 日，价格折扣 – 活动结束前 12 小时
-FBA入仓截止日期：
-欧盟 – 2026年5月27日，英国 – 2026年6月5日
-提报您的促销 &gt; https://go.amazonsellerservices.com/e/229492/reate-ld-DC-EM-D448077710-Wk20/7z3d8gb/6653207154/h/6CLWu2W4fKzXAhce-EQn20MSg278mQHtkVfxmtI7vHk
-&lt;table align="center" border="0" cellpadding="0" cellspacing="0" class="section" role="presentation" style="width:100%;"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td align="center"&gt;
-			&lt;div role="none"&gt;
-&lt;!--[if(mso)|(IE)]&gt;
-&lt;table align="center" border="0" cellpadding="0" cellspacing="0" class="block-grid-outlook" style="width:600px;" width="600" &gt;
-&lt;tr&gt;
-&lt;td style="line-height:0px;font-size:0px;mso-line-height-rule:exactly;"&gt;&lt;![endif]--&gt;
-			&lt;div style="margin:0 auto;border-radius:0px;max-width:600px;"&gt;
-			&lt;table align="center" border="0" cellpadding="0" cellspacing="0" role="presentation" style="width:100%;border-radius:0px;"&gt;
-				&lt;tbody&gt;
-					&lt;tr&gt;
-						&lt;td class="block-grid" style="border-radius:0px;font-size:0px;padding:12px 0px 12px 0px;text-align:center;vertical-align:top;"&gt;
-&lt;!--[if(mso)|(IE)]&gt;
-&lt;table role="presentati</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 13 May 2026 16:40:18 +0000</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F255" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="2" t="inlineStr">
-        <is>
-          <t>Hola Weihai EU,
-Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
-Nuestro equipo de
-análisis ha señalado que una asociación con usted sería una gran oportunidad
-para ambos.
-¿Estaría
-disponible para una reunión online esta semana?
-Acerca de Worten
-- Somos el líder del mercado portugués:
-- Nº 1 del
-comercio electrónico portugués
-- Sitio web con
-mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
-- Más de 200
-tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
-- Plataforma de
-gestión: Mirakl (se puede integrar manualmente o vía API)
-- Sin costes los 6 meses iniciales
-Estaré encantado
-de ayudarle si tiene alguna pregunta.
-Muchas gracias,
-Saludos
-Cordiales</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 04:38:11 +0000</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13666,39 +13233,39 @@
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 03:47:37 +0000</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-18</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr"/>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13722,39 +13289,39 @@
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 20:10:01 +0000</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr"/>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -13770,39 +13337,39 @@
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 04:57:03 +0000</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F259" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-11</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13825,39 +13392,39 @@
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 03:41:21 +0000</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F260" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr"/>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13881,39 +13448,39 @@
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 03:00:56 +0000</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F261" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr"/>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13936,39 +13503,39 @@
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F262" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr"/>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13991,39 +13558,39 @@
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F263" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr"/>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14047,39 +13614,39 @@
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14103,39 +13670,39 @@
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr"/>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14156,39 +13723,39 @@
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr"/>
-      <c r="H266" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14211,39 +13778,39 @@
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:46:25 +0000</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F267" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr"/>
-      <c r="H267" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -14297,39 +13864,39 @@
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 00:17:48 +0000</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F268" s="2" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr"/>
-      <c r="H268" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -14359,40 +13926,40 @@
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F269" s="2" t="inlineStr">
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr">
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
